--- a/public/管理口径原因分析默认模版/南通项目部.xlsx
+++ b/public/管理口径原因分析默认模版/南通项目部.xlsx
@@ -9,21 +9,21 @@
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
     <sheet sheetId="3" name="合计" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="蓝海新材料江苏配餐项目" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="蓝海新材料江苏物业项目" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="华东化工销售江苏物业项目" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="昆仑工程辽阳江苏物业项目" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="江苏南通销售分公司配餐业务" state="visible" r:id="rId10"/>
-    <sheet sheetId="9" name="江苏中石油国际事业有限公司配餐业务" state="visible" r:id="rId11"/>
-    <sheet sheetId="10" name="江苏盐城销售分公司劳务输出" state="visible" r:id="rId12"/>
-    <sheet sheetId="11" name="大连石化江苏配餐项目" state="visible" r:id="rId13"/>
-    <sheet sheetId="12" name="蓝海新材料新市场拓展+提质增效" state="visible" r:id="rId14"/>
-    <sheet sheetId="13" name="蓝海生产管理楼江苏配餐项目" state="visible" r:id="rId15"/>
-    <sheet sheetId="14" name="中油国际事业江苏物业项目" state="visible" r:id="rId16"/>
-    <sheet sheetId="15" name="中油电能江苏配餐项目" state="visible" r:id="rId17"/>
-    <sheet sheetId="16" name="昆仑物流江苏配餐项目" state="visible" r:id="rId18"/>
-    <sheet sheetId="17" name="昆冈制造江苏配餐项目" state="visible" r:id="rId19"/>
-    <sheet sheetId="18" name="兰州石化江苏配餐项目（新）" state="visible" r:id="rId20"/>
+    <sheet sheetId="4" name="蓝海江苏配餐" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="蓝海江苏物业" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="华东化工江苏物业" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="昆仑工程辽阳物业" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="南通配餐" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="中石油国际配餐" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="盐城劳务输出" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="大连石化江苏配餐" state="visible" r:id="rId13"/>
+    <sheet sheetId="12" name="蓝海新市场提质" state="visible" r:id="rId14"/>
+    <sheet sheetId="13" name="蓝海生产楼配餐" state="visible" r:id="rId15"/>
+    <sheet sheetId="14" name="中油国际江苏物业" state="visible" r:id="rId16"/>
+    <sheet sheetId="15" name="中油电能江苏配餐" state="visible" r:id="rId17"/>
+    <sheet sheetId="16" name="昆仑物流江苏配餐" state="visible" r:id="rId18"/>
+    <sheet sheetId="17" name="昆冈制造江苏配餐" state="visible" r:id="rId19"/>
+    <sheet sheetId="18" name="兰州石化江苏配餐" state="visible" r:id="rId20"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -47,49 +47,49 @@
     <t>合计</t>
   </si>
   <si>
-    <t>蓝海新材料江苏配餐项目</t>
+    <t>蓝海江苏配餐</t>
   </si>
   <si>
-    <t>蓝海新材料江苏物业项目</t>
+    <t>蓝海江苏物业</t>
   </si>
   <si>
-    <t>华东化工销售江苏物业项目</t>
+    <t>华东化工江苏物业</t>
   </si>
   <si>
-    <t>昆仑工程辽阳江苏物业项目</t>
+    <t>昆仑工程辽阳物业</t>
   </si>
   <si>
-    <t>江苏南通销售分公司配餐业务</t>
+    <t>南通配餐</t>
   </si>
   <si>
-    <t>江苏中石油国际事业有限公司配餐业务</t>
+    <t>中石油国际配餐</t>
   </si>
   <si>
-    <t>江苏盐城销售分公司劳务输出</t>
+    <t>盐城劳务输出</t>
   </si>
   <si>
-    <t>大连石化江苏配餐项目</t>
+    <t>大连石化江苏配餐</t>
   </si>
   <si>
-    <t>蓝海新材料新市场拓展+提质增效</t>
+    <t>蓝海新市场提质</t>
   </si>
   <si>
-    <t>蓝海生产管理楼江苏配餐项目</t>
+    <t>蓝海生产楼配餐</t>
   </si>
   <si>
-    <t>中油国际事业江苏物业项目</t>
+    <t>中油国际江苏物业</t>
   </si>
   <si>
-    <t>中油电能江苏配餐项目</t>
+    <t>中油电能江苏配餐</t>
   </si>
   <si>
-    <t>昆仑物流江苏配餐项目</t>
+    <t>昆仑物流江苏配餐</t>
   </si>
   <si>
-    <t>昆冈制造江苏配餐项目</t>
+    <t>昆冈制造江苏配餐</t>
   </si>
   <si>
-    <t>兰州石化江苏配餐项目（新）</t>
+    <t>兰州石化江苏配餐</t>
   </si>
   <si>
     <t>合计预算执行分析（2026年08月）</t>
@@ -305,7 +305,7 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>蓝海新材料江苏配餐项目预算执行分析（2026年08月）</t>
+    <t>蓝海江苏配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>蓝海配餐收入比同期增加267.29万元，主要是该项目25年存在部分收入延后确认的情况，基数相对较低。</t>
@@ -326,7 +326,7 @@
     <t>蓝海配餐利润比预算增加66.74万元，因为蓝海公司在岗员工人数增加，食堂就餐人数增多，规模扩张推动利润提升。</t>
   </si>
   <si>
-    <t>蓝海新材料江苏物业项目预算执行分析（2026年08月）</t>
+    <t>蓝海江苏物业预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>蓝海物业收入比同期增加251.37万元，主要是该项目25年存在部分收入延后确认的情况，基数相对较低。</t>
@@ -350,7 +350,7 @@
     <t>蓝海物业绿化环境卫生费比预算增加32.57万元，因为1.随着蓝海公司厂区的建设和使用，垃圾桶数量由预算的9个增长至58个；2.项目部拓展了洒水排污服务，收入增加的同时成本随之增加。</t>
   </si>
   <si>
-    <t>华东化工销售江苏物业项目预算执行分析（2026年08月）</t>
+    <t>华东化工江苏物业预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>去年同期未新增WBS</t>
@@ -359,13 +359,13 @@
     <t>华东化工物业人工成本比预算增加0.66万元，主要是按客户要求，将人员工资由原来的5500元/月，上涨至7200元/月。</t>
   </si>
   <si>
-    <t>昆仑工程辽阳江苏物业项目预算执行分析（2026年08月）</t>
+    <t>昆仑工程辽阳物业预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新增项目</t>
   </si>
   <si>
-    <t>江苏南通销售分公司配餐业务预算执行分析（2026年08月）</t>
+    <t>南通配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>南通销售配餐收入比同期增加6.36万元，主要是因为1.25年5月的收入和成本延后入账；2.南通销售要求调增餐标，收入增加。</t>
@@ -377,7 +377,7 @@
     <t>调增餐标使得食材成本增加。</t>
   </si>
   <si>
-    <t>江苏中石油国际事业有限公司配餐业务预算执行分析（2026年08月）</t>
+    <t>中石油国际配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>中油国际配餐收入比同期增加1.57万元，主要是因为25年5月的收入和成本延后入账。</t>
@@ -386,7 +386,7 @@
     <t>中油国际配餐收入比预算增加0.96万元，主要是因为就餐人数比预算增加了1人。</t>
   </si>
   <si>
-    <t>江苏盐城销售分公司劳务输出预算执行分析（2026年08月）</t>
+    <t>盐城劳务输出预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>盐城销售配餐收入比同期增加5.8万元，主要是因为25年5月的收入和成本延后入账。</t>
@@ -395,7 +395,7 @@
     <t>盐城销售配餐收入比预算增加2.53万元，主要是因为续签合同时，调增了服务人员的工资标准。</t>
   </si>
   <si>
-    <t>大连石化江苏配餐项目预算执行分析（2026年08月）</t>
+    <t>大连石化江苏配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>大连石化配餐收入比预算增加124.68万元，因为1.大连石化公司内部流程原因导致延迟确认了2025年11~12月的收入约79万元，故相对应的收入于2026年2月到账，使得收入增加，2.大连石化就餐人数逐渐增加，收入增加。</t>
@@ -407,10 +407,10 @@
     <t>大连石化配餐利润比预算增加61.31万元，因为25年收入的延迟入账，以及食堂就餐人数增多，使得利润提升。</t>
   </si>
   <si>
-    <t>蓝海新材料新市场拓展+提质增效预算执行分析（2026年08月）</t>
+    <t>蓝海新市场提质预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>蓝海生产管理楼江苏配餐项目预算执行分析（2026年08月）</t>
+    <t>蓝海生产楼配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>蓝海三食堂配餐收入比预算增加18.48万元，主要是因为预算未包含代采的设施设备约15.5万元。</t>
@@ -422,19 +422,19 @@
     <t>投标费用</t>
   </si>
   <si>
-    <t>中油国际事业江苏物业项目预算执行分析（2026年08月）</t>
+    <t>中油国际江苏物业预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中油电能江苏配餐项目预算执行分析（2026年08月）</t>
+    <t>中油电能江苏配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>昆仑物流江苏配餐项目预算执行分析（2026年08月）</t>
+    <t>昆仑物流江苏配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>昆冈制造江苏配餐项目预算执行分析（2026年08月）</t>
+    <t>昆冈制造江苏配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>兰州石化江苏配餐项目（新）预算执行分析（2026年08月）</t>
+    <t>兰州石化江苏配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>新开设WBS项目</t>
@@ -7892,7 +7892,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="str">
-        <f>HYPERLINK("#'蓝海新材料江苏配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'蓝海江苏配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7902,7 +7902,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>HYPERLINK("#'蓝海新材料江苏物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'蓝海江苏物业'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f>HYPERLINK("#'华东化工销售江苏物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'华东化工江苏物业'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>HYPERLINK("#'昆仑工程辽阳江苏物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'昆仑工程辽阳物业'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7932,7 +7932,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f>HYPERLINK("#'江苏南通销售分公司配餐业务'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'南通配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f>HYPERLINK("#'江苏中石油国际事业有限公司配餐业务'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'中石油国际配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7952,7 +7952,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="5" t="str">
-        <f>HYPERLINK("#'江苏盐城销售分公司劳务输出'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'盐城劳务输出'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f>HYPERLINK("#'大连石化江苏配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'大连石化江苏配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="5" t="str">
-        <f>HYPERLINK("#'蓝海新材料新市场拓展+提质增效'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'蓝海新市场提质'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f>HYPERLINK("#'蓝海生产管理楼江苏配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'蓝海生产楼配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="5" t="str">
-        <f>HYPERLINK("#'中油国际事业江苏物业项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'中油国际江苏物业'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="5" t="str">
-        <f>HYPERLINK("#'中油电能江苏配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'中油电能江苏配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="5" t="str">
-        <f>HYPERLINK("#'昆仑物流江苏配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'昆仑物流江苏配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8022,7 +8022,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="5" t="str">
-        <f>HYPERLINK("#'昆冈制造江苏配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'昆冈制造江苏配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8032,7 +8032,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="5" t="str">
-        <f>HYPERLINK("#'兰州石化江苏配餐项目（新）'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'兰州石化江苏配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
